--- a/data/dividends_info_20260528.xlsx
+++ b/data/dividends_info_20260528.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>59.45000076293945</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.151387718830956</v>
+        <v>0.1505016741609309</v>
       </c>
       <c r="J2" t="n">
         <v>291</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>54.15000152587891</v>
+        <v>54.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.292705411403289</v>
+        <v>1.293900221337062</v>
       </c>
       <c r="J3" t="n">
         <v>270</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6564551175737441</v>
       </c>
       <c r="J4" t="n">
         <v>200</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>59.45999908447266</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1513622626736678</v>
+        <v>0.1505016741609309</v>
       </c>
       <c r="J6" t="n">
         <v>200</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.70499992370605</v>
+        <v>22.63999938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.189165386070298</v>
+        <v>1.192579537451095</v>
       </c>
       <c r="J8" t="n">
         <v>179</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.599999904632568</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="I9" t="n">
-        <v>3.571428632249639</v>
+        <v>3.514938453229105</v>
       </c>
       <c r="J9" t="n">
         <v>172</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8391608279680262</v>
       </c>
       <c r="J10" t="n">
         <v>144</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.239999771118164</v>
+        <v>5.420000076293945</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9541985149615856</v>
+        <v>0.9225092121066666</v>
       </c>
       <c r="J12" t="n">
         <v>130</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.960000038146973</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J13" t="n">
         <v>123</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.70999908447266</v>
+        <v>22.63999938964844</v>
       </c>
       <c r="I14" t="n">
-        <v>1.188903614639972</v>
+        <v>1.192579537451095</v>
       </c>
       <c r="J14" t="n">
         <v>116</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>59.45999908447266</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1513622626736678</v>
+        <v>0.1505016741609309</v>
       </c>
       <c r="J15" t="n">
         <v>116</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.699999809265137</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I16" t="n">
-        <v>5.263158070853988</v>
+        <v>4.918032863773797</v>
       </c>
       <c r="J16" t="n">
         <v>109</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.960000038146973</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J18" t="n">
         <v>67</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.900000095367432</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I19" t="n">
-        <v>4.237288067101817</v>
+        <v>4.244482269388714</v>
       </c>
       <c r="J19" t="n">
         <v>60</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.602999687194824</v>
+        <v>9.597000122070312</v>
       </c>
       <c r="I20" t="n">
-        <v>2.70748733176258</v>
+        <v>2.709179917608582</v>
       </c>
       <c r="J20" t="n">
         <v>53</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14.88000011444092</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="I21" t="n">
-        <v>4.032258033504347</v>
+        <v>4.02144770061581</v>
       </c>
       <c r="J21" t="n">
         <v>53</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.667999982833862</v>
+        <v>3.674000024795532</v>
       </c>
       <c r="I22" t="n">
-        <v>5.997819002987837</v>
+        <v>5.988023911683114</v>
       </c>
       <c r="J22" t="n">
         <v>53</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.260000228881836</v>
+        <v>6.275000095367432</v>
       </c>
       <c r="I24" t="n">
-        <v>3.833865674520413</v>
+        <v>3.824701137091327</v>
       </c>
       <c r="J24" t="n">
         <v>53</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18.95000076293945</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="I25" t="n">
-        <v>1.984168785551417</v>
+        <v>2.049046278929203</v>
       </c>
       <c r="J25" t="n">
         <v>53</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.200000047683716</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I29" t="n">
-        <v>3.863636279894303</v>
+        <v>3.899082449407415</v>
       </c>
       <c r="J29" t="n">
         <v>39</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.369999885559082</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="I30" t="n">
-        <v>1.601830705564068</v>
+        <v>1.548672572906767</v>
       </c>
       <c r="J30" t="n">
         <v>39</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31.45000076293945</v>
+        <v>31.60000038146973</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4769475242008876</v>
+        <v>0.4746835385735</v>
       </c>
       <c r="J31" t="n">
         <v>39</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>22.94000053405762</v>
+        <v>22.76000022888184</v>
       </c>
       <c r="I33" t="n">
-        <v>4.141237915795132</v>
+        <v>4.173989413209562</v>
       </c>
       <c r="J33" t="n">
         <v>25</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>30.75</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6414473764701565</v>
       </c>
       <c r="J34" t="n">
         <v>25</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.870000004768372</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="I35" t="n">
-        <v>1.764705877853063</v>
+        <v>1.736842127057654</v>
       </c>
       <c r="J35" t="n">
         <v>25</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.375</v>
+        <v>5.385000228881836</v>
       </c>
       <c r="I36" t="n">
-        <v>5.395348837209301</v>
+        <v>5.385329390417069</v>
       </c>
       <c r="J36" t="n">
         <v>25</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.888000011444092</v>
+        <v>3.854000091552734</v>
       </c>
       <c r="I37" t="n">
-        <v>4.115226325335641</v>
+        <v>4.151530778390245</v>
       </c>
       <c r="J37" t="n">
         <v>25</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.733999967575073</v>
+        <v>2.696000099182129</v>
       </c>
       <c r="I38" t="n">
-        <v>5.069495305185813</v>
+        <v>5.140949365767692</v>
       </c>
       <c r="J38" t="n">
         <v>25</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>54.34999847412109</v>
+        <v>54.41999816894531</v>
       </c>
       <c r="I39" t="n">
-        <v>1.159153666397942</v>
+        <v>1.157662662986837</v>
       </c>
       <c r="J39" t="n">
         <v>25</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.454999923706055</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I40" t="n">
-        <v>2.566452831494924</v>
+        <v>2.500000042574747</v>
       </c>
       <c r="J40" t="n">
         <v>25</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.54999923706055</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="I41" t="n">
-        <v>3.989769976672784</v>
+        <v>3.91959806508583</v>
       </c>
       <c r="J41" t="n">
         <v>25</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>25.07999992370605</v>
+        <v>25.02000045776367</v>
       </c>
       <c r="I42" t="n">
-        <v>3.389154715254066</v>
+        <v>3.397282112104223</v>
       </c>
       <c r="J42" t="n">
         <v>25</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>59.45999908447266</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1513622626736678</v>
+        <v>0.1505016741609309</v>
       </c>
       <c r="J43" t="n">
         <v>25</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.409999966621399</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="I44" t="n">
-        <v>0.709219874945225</v>
+        <v>0.6944444168497026</v>
       </c>
       <c r="J44" t="n">
         <v>25</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.302000045776367</v>
+        <v>6.26800012588501</v>
       </c>
       <c r="I45" t="n">
-        <v>2.876864466567374</v>
+        <v>2.892469629208907</v>
       </c>
       <c r="J45" t="n">
         <v>25</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.819999694824219</v>
+        <v>8.930000305175781</v>
       </c>
       <c r="I46" t="n">
-        <v>2.947845906985394</v>
+        <v>2.91153405503587</v>
       </c>
       <c r="J46" t="n">
         <v>25</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.928000450134277</v>
+        <v>9.85200023651123</v>
       </c>
       <c r="I47" t="n">
-        <v>2.79008851169274</v>
+        <v>2.811611787964093</v>
       </c>
       <c r="J47" t="n">
         <v>25</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.039999961853027</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="I48" t="n">
-        <v>1.298076970690103</v>
+        <v>1.285714344102512</v>
       </c>
       <c r="J48" t="n">
         <v>18</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.022000074386597</v>
+        <v>3.003999948501587</v>
       </c>
       <c r="I49" t="n">
-        <v>3.639973437867229</v>
+        <v>3.661784350391506</v>
       </c>
       <c r="J49" t="n">
         <v>18</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.875</v>
       </c>
       <c r="I52" t="n">
-        <v>2.808988809194278</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J52" t="n">
         <v>11</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28.89999961853027</v>
+        <v>29</v>
       </c>
       <c r="I53" t="n">
-        <v>3.840830500524587</v>
+        <v>3.827586206896552</v>
       </c>
       <c r="J53" t="n">
         <v>7</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.9229999780654907</v>
+        <v>0.8980000019073486</v>
       </c>
       <c r="I54" t="n">
-        <v>3.250270933145285</v>
+        <v>3.340757231211593</v>
       </c>
       <c r="J54" t="n">
         <v>4</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5270000100135803</v>
       </c>
       <c r="I55" t="n">
-        <v>4.423077085314424</v>
+        <v>4.364326292784569</v>
       </c>
       <c r="J55" t="n">
         <v>4</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.345000028610229</v>
+        <v>2.375</v>
       </c>
       <c r="I58" t="n">
-        <v>7.675906089718791</v>
+        <v>7.578947368421051</v>
       </c>
       <c r="J58" t="n">
         <v>-3</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I59" t="n">
-        <v>3.75</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J59" t="n">
         <v>-3</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15.10999965667725</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="I60" t="n">
-        <v>1.654533459168695</v>
+        <v>1.646903787707829</v>
       </c>
       <c r="J60" t="n">
         <v>-3</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.640000104904175</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8241758004232191</v>
+        <v>0.8310249548969494</v>
       </c>
       <c r="J61" t="n">
         <v>-3</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.099999904632568</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="I62" t="n">
-        <v>3.658536670464694</v>
+        <v>3.676470656983444</v>
       </c>
       <c r="J62" t="n">
         <v>-3</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13.25</v>
+        <v>13.19999980926514</v>
       </c>
       <c r="I63" t="n">
-        <v>4.377358490566038</v>
+        <v>4.393939457430109</v>
       </c>
       <c r="J63" t="n">
         <v>-3</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.265000104904175</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I64" t="n">
-        <v>4.591611266366804</v>
+        <v>4.601769930922964</v>
       </c>
       <c r="J64" t="n">
         <v>-10</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.93000030517578</v>
+        <v>11.01500034332275</v>
       </c>
       <c r="I65" t="n">
-        <v>2.65324786736441</v>
+        <v>2.632773408634497</v>
       </c>
       <c r="J65" t="n">
         <v>-10</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>38.29999923706055</v>
+        <v>38.33000183105469</v>
       </c>
       <c r="I67" t="n">
-        <v>4.281984419501171</v>
+        <v>4.27863272020844</v>
       </c>
       <c r="J67" t="n">
         <v>-10</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>34.84999847412109</v>
+        <v>34.72999954223633</v>
       </c>
       <c r="I68" t="n">
-        <v>5.738881169493191</v>
+        <v>5.758710124852528</v>
       </c>
       <c r="J68" t="n">
         <v>-10</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3.295000076293945</v>
+        <v>3.279999971389771</v>
       </c>
       <c r="I69" t="n">
-        <v>3.034901295434115</v>
+        <v>3.048780514398266</v>
       </c>
       <c r="J69" t="n">
         <v>-10</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>43.7599983215332</v>
+        <v>43.86000061035156</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3392596108189212</v>
+        <v>0.3384860874009231</v>
       </c>
       <c r="J70" t="n">
         <v>-10</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>20.13999938964844</v>
+        <v>20.26000022888184</v>
       </c>
       <c r="I71" t="n">
-        <v>4.568023971603802</v>
+        <v>4.540967372194228</v>
       </c>
       <c r="J71" t="n">
         <v>-10</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>11.76000022888184</v>
+        <v>11.77000045776367</v>
       </c>
       <c r="I72" t="n">
-        <v>2.551020358513416</v>
+        <v>2.548852917011702</v>
       </c>
       <c r="J72" t="n">
         <v>-10</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>83.26000213623047</v>
+        <v>81.63999938964844</v>
       </c>
       <c r="I73" t="n">
-        <v>1.249099175253859</v>
+        <v>1.273885359842209</v>
       </c>
       <c r="J73" t="n">
         <v>-10</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>45.61000061035156</v>
+        <v>45.88999938964844</v>
       </c>
       <c r="I74" t="n">
-        <v>1.534751130525373</v>
+        <v>1.525386814796736</v>
       </c>
       <c r="J74" t="n">
         <v>-10</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>54.15000152587891</v>
+        <v>54.09999847412109</v>
       </c>
       <c r="I75" t="n">
-        <v>4.062788435838907</v>
+        <v>4.066543552773624</v>
       </c>
       <c r="J75" t="n">
         <v>-10</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.97599983215332</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="I76" t="n">
-        <v>9.581105348502309</v>
+        <v>9.429824679732214</v>
       </c>
       <c r="J76" t="n">
         <v>-10</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.58600044250488</v>
+        <v>11.67199993133545</v>
       </c>
       <c r="I77" t="n">
-        <v>4.833419459795295</v>
+        <v>4.797806745154151</v>
       </c>
       <c r="J77" t="n">
         <v>-10</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.150000095367432</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I78" t="n">
-        <v>1.860465033754525</v>
+        <v>1.843317907541938</v>
       </c>
       <c r="J78" t="n">
         <v>-10</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>9.050000190734863</v>
+        <v>9</v>
       </c>
       <c r="I79" t="n">
-        <v>3.314917057207707</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J79" t="n">
         <v>-10</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>88.69999694824219</v>
+        <v>89</v>
       </c>
       <c r="I81" t="n">
-        <v>2.322435254650619</v>
+        <v>2.314606741573034</v>
       </c>
       <c r="J81" t="n">
         <v>-10</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>15.15999984741211</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="I82" t="n">
-        <v>4.947229601245866</v>
+        <v>4.943968333737979</v>
       </c>
       <c r="J82" t="n">
         <v>-10</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>14.44999980926514</v>
+        <v>14.36999988555908</v>
       </c>
       <c r="I83" t="n">
-        <v>2.076124594878155</v>
+        <v>2.087682688859869</v>
       </c>
       <c r="J83" t="n">
         <v>-10</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>51.59999847412109</v>
+        <v>52</v>
       </c>
       <c r="I84" t="n">
-        <v>1.647286870417835</v>
+        <v>1.634615384615385</v>
       </c>
       <c r="J84" t="n">
         <v>-10</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>35.13999938964844</v>
+        <v>35.15999984741211</v>
       </c>
       <c r="I85" t="n">
-        <v>2.418895887204806</v>
+        <v>2.417519919479075</v>
       </c>
       <c r="J85" t="n">
         <v>-10</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>65.77999877929688</v>
+        <v>66.80000305175781</v>
       </c>
       <c r="I86" t="n">
-        <v>1.976284621654862</v>
+        <v>1.946107695523213</v>
       </c>
       <c r="J86" t="n">
         <v>-10</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.400000095367432</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="I88" t="n">
-        <v>7.343749890569598</v>
+        <v>7.175572310132548</v>
       </c>
       <c r="J88" t="n">
         <v>-10</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.599999904632568</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="I89" t="n">
-        <v>3.571428632249639</v>
+        <v>3.514938453229105</v>
       </c>
       <c r="J89" t="n">
         <v>-10</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.23999977111816</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I90" t="n">
-        <v>4.302926032050844</v>
+        <v>4.30663234096166</v>
       </c>
       <c r="J90" t="n">
         <v>-10</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.599999904632568</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="I91" t="n">
-        <v>4.673913140378064</v>
+        <v>4.613734056652349</v>
       </c>
       <c r="J91" t="n">
         <v>-10</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>22.70999908447266</v>
+        <v>22.63999938964844</v>
       </c>
       <c r="I92" t="n">
-        <v>1.188903614639972</v>
+        <v>1.192579537451095</v>
       </c>
       <c r="J92" t="n">
         <v>-10</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.399999618530273</v>
+        <v>9.720000267028809</v>
       </c>
       <c r="I93" t="n">
-        <v>2.127659660812527</v>
+        <v>2.057613112197328</v>
       </c>
       <c r="J93" t="n">
         <v>-10</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.805000305175781</v>
+        <v>8.779999732971191</v>
       </c>
       <c r="I94" t="n">
-        <v>2.725723925971047</v>
+        <v>2.733485276756186</v>
       </c>
       <c r="J94" t="n">
         <v>-10</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>20.65999984741211</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="I95" t="n">
-        <v>3.823814161832902</v>
+        <v>3.83495138529525</v>
       </c>
       <c r="J95" t="n">
         <v>-10</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8391608279680262</v>
       </c>
       <c r="J97" t="n">
         <v>-10</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>36.09999847412109</v>
+        <v>35.61999893188477</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9695291268527435</v>
+        <v>0.9825940777519286</v>
       </c>
       <c r="J98" t="n">
         <v>-10</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6.775000095367432</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="I99" t="n">
-        <v>8.181549700331605</v>
+        <v>8.236255548723015</v>
       </c>
       <c r="J99" t="n">
         <v>-10</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>13</v>
+        <v>12.94999980926514</v>
       </c>
       <c r="I101" t="n">
-        <v>1.538461538461539</v>
+        <v>1.544401567148357</v>
       </c>
       <c r="J101" t="n">
         <v>-10</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>7.78000020980835</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="I102" t="n">
-        <v>1.323907419310176</v>
+        <v>1.33419692745151</v>
       </c>
       <c r="J102" t="n">
         <v>-10</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5.739999771118164</v>
+        <v>5.749000072479248</v>
       </c>
       <c r="I103" t="n">
-        <v>3.310104661606765</v>
+        <v>3.304922553567872</v>
       </c>
       <c r="J103" t="n">
         <v>-10</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>10.24499988555908</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="I104" t="n">
-        <v>4.216691115916252</v>
+        <v>4.260354885337597</v>
       </c>
       <c r="J104" t="n">
         <v>-10</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>25.20000076293945</v>
+        <v>25.30999946594238</v>
       </c>
       <c r="I105" t="n">
-        <v>1.746031693169982</v>
+        <v>1.738443339724572</v>
       </c>
       <c r="J105" t="n">
         <v>-10</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1.070000052452087</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="I106" t="n">
-        <v>2.803738180315963</v>
+        <v>2.88461549042245</v>
       </c>
       <c r="J106" t="n">
         <v>-10</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>7.050000190734863</v>
+        <v>7</v>
       </c>
       <c r="I107" t="n">
-        <v>6.666666486302734</v>
+        <v>6.714285714285714</v>
       </c>
       <c r="J107" t="n">
         <v>-10</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>54.47999954223633</v>
+        <v>55.38000106811523</v>
       </c>
       <c r="I108" t="n">
-        <v>2.569750388699309</v>
+        <v>2.527988394724035</v>
       </c>
       <c r="J108" t="n">
         <v>-10</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.484999895095825</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I109" t="n">
-        <v>8.608321636455919</v>
+        <v>8.720930087495459</v>
       </c>
       <c r="J109" t="n">
         <v>-10</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>3.220000028610229</v>
+        <v>3.25</v>
       </c>
       <c r="I111" t="n">
-        <v>5.27950305868081</v>
+        <v>5.230769230769231</v>
       </c>
       <c r="J111" t="n">
         <v>-10</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>22.75</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="I112" t="n">
-        <v>3.076923076923077</v>
+        <v>3.063457279272813</v>
       </c>
       <c r="J112" t="n">
         <v>-10</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.610000133514404</v>
+        <v>5.579999923706055</v>
       </c>
       <c r="I114" t="n">
-        <v>5.882352801180245</v>
+        <v>5.913978575484007</v>
       </c>
       <c r="J114" t="n">
         <v>-10</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.8889999985694885</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I115" t="n">
-        <v>7.874015760701766</v>
+        <v>7.777777983818532</v>
       </c>
       <c r="J115" t="n">
         <v>-10</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I119" t="n">
-        <v>1.153846153846154</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="J119" t="n">
         <v>-10</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>4.10699987411499</v>
+        <v>4.166999816894531</v>
       </c>
       <c r="I120" t="n">
-        <v>4.139274536418947</v>
+        <v>4.079673805378111</v>
       </c>
       <c r="J120" t="n">
         <v>-10</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>57.40000152587891</v>
+        <v>57.29999923706055</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7839721045950089</v>
+        <v>0.7853403245927945</v>
       </c>
       <c r="J122" t="n">
         <v>-10</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.659999847412109</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7067137999710191</v>
+        <v>0.6968641392856347</v>
       </c>
       <c r="J123" t="n">
         <v>-10</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>37.40000152587891</v>
+        <v>37.61999893188477</v>
       </c>
       <c r="I124" t="n">
-        <v>2.807486516473678</v>
+        <v>2.791068659786894</v>
       </c>
       <c r="J124" t="n">
         <v>-10</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>17.64999961853027</v>
+        <v>17.68000030517578</v>
       </c>
       <c r="I126" t="n">
-        <v>2.152974550781565</v>
+        <v>2.149321229868734</v>
       </c>
       <c r="J126" t="n">
         <v>-10</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>26.07999992370605</v>
+        <v>25.8799991607666</v>
       </c>
       <c r="I127" t="n">
-        <v>2.300613503662687</v>
+        <v>2.318392656324287</v>
       </c>
       <c r="J127" t="n">
         <v>-10</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>35.45000076293945</v>
+        <v>36.04999923706055</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9873060436317422</v>
+        <v>0.9708738069547276</v>
       </c>
       <c r="J128" t="n">
         <v>-10</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>3.200000047683716</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5312499920837582</v>
+        <v>0.5379746689320455</v>
       </c>
       <c r="J129" t="n">
         <v>-10</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2.855000019073486</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3502626946827563</v>
+        <v>0.3533568999855096</v>
       </c>
       <c r="J130" t="n">
         <v>-10</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>21.19000053405762</v>
+        <v>21.03000068664551</v>
       </c>
       <c r="I131" t="n">
-        <v>5.285511900766028</v>
+        <v>5.325724980652158</v>
       </c>
       <c r="J131" t="n">
         <v>-10</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2.190000057220459</v>
+        <v>2.216000080108643</v>
       </c>
       <c r="I134" t="n">
-        <v>4.214611762026474</v>
+        <v>4.165162304302573</v>
       </c>
       <c r="J134" t="n">
         <v>-10</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>9.199999809265137</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="I135" t="n">
-        <v>3.804347904958889</v>
+        <v>3.837719346402645</v>
       </c>
       <c r="J135" t="n">
         <v>-17</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>5.25</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I136" t="n">
-        <v>1.828571428571429</v>
+        <v>1.846153913870368</v>
       </c>
       <c r="J136" t="n">
         <v>-17</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>11.60000038146973</v>
+        <v>11.5</v>
       </c>
       <c r="I138" t="n">
-        <v>1.724137874335655</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="J138" t="n">
         <v>-17</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.100000381469727</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6564551175737441</v>
       </c>
       <c r="J139" t="n">
         <v>-17</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>15.18000030517578</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="I142" t="n">
-        <v>3.293807575415659</v>
+        <v>3.311258194493725</v>
       </c>
       <c r="J142" t="n">
         <v>-17</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.289999961853027</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I144" t="n">
-        <v>3.343465084359596</v>
+        <v>3.333333381498703</v>
       </c>
       <c r="J144" t="n">
         <v>-17</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1.269999980926514</v>
+        <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>2.362204759886205</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>-17</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>7.329999923706055</v>
+        <v>7.360000133514404</v>
       </c>
       <c r="I150" t="n">
-        <v>3.001364287719771</v>
+        <v>2.989130380558157</v>
       </c>
       <c r="J150" t="n">
         <v>-17</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>24.60000038146973</v>
+        <v>24.54999923706055</v>
       </c>
       <c r="I151" t="n">
-        <v>2.4796747582959</v>
+        <v>2.484725128134209</v>
       </c>
       <c r="J151" t="n">
         <v>-24</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>2.740000009536743</v>
+        <v>2.759999990463257</v>
       </c>
       <c r="I152" t="n">
-        <v>5.474452535690348</v>
+        <v>5.434782627474683</v>
       </c>
       <c r="J152" t="n">
         <v>-24</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.5</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I153" t="n">
-        <v>6.08695652173913</v>
+        <v>6.034482560174792</v>
       </c>
       <c r="J153" t="n">
         <v>-24</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>7.474999904632568</v>
+        <v>7.335000038146973</v>
       </c>
       <c r="I155" t="n">
-        <v>3.61204017986234</v>
+        <v>3.680981575948425</v>
       </c>
       <c r="J155" t="n">
         <v>-24</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>6.755000114440918</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="I156" t="n">
-        <v>5.181347062478443</v>
+        <v>5.223880745727788</v>
       </c>
       <c r="J156" t="n">
         <v>-24</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I157" t="n">
-        <v>2.5</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="J157" t="n">
         <v>-24</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>17.14999961853027</v>
+        <v>17.25</v>
       </c>
       <c r="I158" t="n">
-        <v>4.373177939838775</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="J158" t="n">
         <v>-24</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>10.89999961853027</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="I159" t="n">
-        <v>3.94495426650281</v>
+        <v>3.788546128174832</v>
       </c>
       <c r="J159" t="n">
         <v>-24</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>4.505000114440918</v>
+        <v>4.525000095367432</v>
       </c>
       <c r="I160" t="n">
-        <v>3.329633655705586</v>
+        <v>3.314917057207707</v>
       </c>
       <c r="J160" t="n">
         <v>-24</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>12.53999996185303</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="I161" t="n">
-        <v>1.572320578945715</v>
+        <v>1.597803870031967</v>
       </c>
       <c r="J161" t="n">
         <v>-24</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>28.54999923706055</v>
+        <v>28.5</v>
       </c>
       <c r="I162" t="n">
-        <v>3.852889770210915</v>
+        <v>3.859649122807018</v>
       </c>
       <c r="J162" t="n">
         <v>-24</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>65.80000305175781</v>
+        <v>66.30000305175781</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7142856811576458</v>
+        <v>0.7088989115627784</v>
       </c>
       <c r="J163" t="n">
         <v>-24</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>87.59999847412109</v>
+        <v>89.40000152587891</v>
       </c>
       <c r="I164" t="n">
-        <v>1.369863037559876</v>
+        <v>1.342281856284568</v>
       </c>
       <c r="J164" t="n">
         <v>-24</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>22.79999923706055</v>
+        <v>23.04999923706055</v>
       </c>
       <c r="I165" t="n">
-        <v>1.184210565942147</v>
+        <v>1.171366633131532</v>
       </c>
       <c r="J165" t="n">
         <v>-24</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>10.35000038146973</v>
+        <v>10.25</v>
       </c>
       <c r="I166" t="n">
-        <v>3.671497449220761</v>
+        <v>3.707317073170731</v>
       </c>
       <c r="J166" t="n">
         <v>-24</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>32.40000152587891</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9259258823194205</v>
+        <v>0.9188360979469335</v>
       </c>
       <c r="J167" t="n">
         <v>-24</v>
@@ -10283,78 +10283,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ATON Green Storage S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Casta Diva Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Telmes S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>